--- a/data/RAD.MI.xlsx
+++ b/data/RAD.MI.xlsx
@@ -42048,6 +42048,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1813">
+      <c r="A1813" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1813" t="n">
+        <v>500</v>
+      </c>
+      <c r="C1813" t="n">
+        <v>0.894999980926514</v>
+      </c>
+      <c r="D1813" t="n">
+        <v>0.894999980926514</v>
+      </c>
+      <c r="E1813" t="n">
+        <v>0.894999980926514</v>
+      </c>
+      <c r="F1813" t="n">
+        <v>0.894999980926514</v>
+      </c>
+      <c r="G1813" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RAD.MI.xlsx
+++ b/data/RAD.MI.xlsx
@@ -42071,6 +42071,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1814">
+      <c r="A1814" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1814" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C1814" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="D1814" t="n">
+        <v>0.865000009536743</v>
+      </c>
+      <c r="E1814" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="F1814" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="G1814" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RAD.MI.xlsx
+++ b/data/RAD.MI.xlsx
@@ -42094,6 +42094,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1815">
+      <c r="A1815" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1815" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C1815" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="D1815" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="E1815" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="F1815" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="G1815" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RAD.MI.xlsx
+++ b/data/RAD.MI.xlsx
@@ -41958,7 +41958,7 @@
     </row>
     <row r="1809">
       <c r="A1809" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1809" t="n">
         <v>0</v>
@@ -41981,22 +41981,22 @@
     </row>
     <row r="1810">
       <c r="A1810" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1810" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="C1810" t="n">
-        <v>0.894999980926514</v>
+        <v>0.920000016689301</v>
       </c>
       <c r="D1810" t="n">
-        <v>0.894999980926514</v>
+        <v>0.920000016689301</v>
       </c>
       <c r="E1810" t="n">
-        <v>0.894999980926514</v>
+        <v>0.920000016689301</v>
       </c>
       <c r="F1810" t="n">
-        <v>0.894999980926514</v>
+        <v>0.920000016689301</v>
       </c>
       <c r="G1810" t="s">
         <v>7</v>
@@ -42004,10 +42004,10 @@
     </row>
     <row r="1811">
       <c r="A1811" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1811" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="C1811" t="n">
         <v>0.894999980926514</v>
@@ -42027,10 +42027,10 @@
     </row>
     <row r="1812">
       <c r="A1812" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1812" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C1812" t="n">
         <v>0.894999980926514</v>
@@ -42050,10 +42050,10 @@
     </row>
     <row r="1813">
       <c r="A1813" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1813" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="C1813" t="n">
         <v>0.894999980926514</v>
@@ -42073,22 +42073,22 @@
     </row>
     <row r="1814">
       <c r="A1814" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1814" t="n">
-        <v>11000</v>
+        <v>500</v>
       </c>
       <c r="C1814" t="n">
-        <v>0.889999985694885</v>
+        <v>0.894999980926514</v>
       </c>
       <c r="D1814" t="n">
-        <v>0.865000009536743</v>
+        <v>0.894999980926514</v>
       </c>
       <c r="E1814" t="n">
-        <v>0.889999985694885</v>
+        <v>0.894999980926514</v>
       </c>
       <c r="F1814" t="n">
-        <v>0.889999985694885</v>
+        <v>0.894999980926514</v>
       </c>
       <c r="G1814" t="s">
         <v>7</v>
@@ -42096,16 +42096,16 @@
     </row>
     <row r="1815">
       <c r="A1815" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1815" t="n">
-        <v>1500</v>
+        <v>11000</v>
       </c>
       <c r="C1815" t="n">
         <v>0.889999985694885</v>
       </c>
       <c r="D1815" t="n">
-        <v>0.889999985694885</v>
+        <v>0.865000009536743</v>
       </c>
       <c r="E1815" t="n">
         <v>0.889999985694885</v>
@@ -42114,6 +42114,52 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1815" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="A1816" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1816" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C1816" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="D1816" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="E1816" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="F1816" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="G1816" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="A1817" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1817" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1817" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="D1817" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="E1817" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="F1817" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="G1817" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RAD.MI.xlsx
+++ b/data/RAD.MI.xlsx
@@ -42142,10 +42142,10 @@
     </row>
     <row r="1817">
       <c r="A1817" s="1" t="n">
-        <v>46283.2916666667</v>
+        <v>46282.2916666667</v>
       </c>
       <c r="B1817" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C1817" t="n">
         <v>0.889999985694885</v>
@@ -42160,6 +42160,29 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1817" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1818">
+      <c r="A1818" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1818" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1818" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="D1818" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="E1818" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="F1818" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="G1818" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RAD.MI.xlsx
+++ b/data/RAD.MI.xlsx
@@ -47695,6 +47695,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1821">
+      <c r="A1821" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1821" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C1821" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="D1821" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="E1821" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="F1821" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="G1821" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="H1821" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RAD.MI.xlsx
+++ b/data/RAD.MI.xlsx
@@ -47721,6 +47721,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1822">
+      <c r="A1822" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1822" t="n">
+        <v>8500</v>
+      </c>
+      <c r="C1822" t="n">
+        <v>0.879999995231628</v>
+      </c>
+      <c r="D1822" t="n">
+        <v>0.879999995231628</v>
+      </c>
+      <c r="E1822" t="n">
+        <v>0.879999995231628</v>
+      </c>
+      <c r="F1822" t="n">
+        <v>0.879999995231628</v>
+      </c>
+      <c r="G1822" t="n">
+        <v>0.879999995231628</v>
+      </c>
+      <c r="H1822" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RAD.MI.xlsx
+++ b/data/RAD.MI.xlsx
@@ -47747,6 +47747,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1823">
+      <c r="A1823" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1823" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C1823" t="n">
+        <v>0.870000004768372</v>
+      </c>
+      <c r="D1823" t="n">
+        <v>0.865000009536743</v>
+      </c>
+      <c r="E1823" t="n">
+        <v>0.865000009536743</v>
+      </c>
+      <c r="F1823" t="n">
+        <v>0.870000004768372</v>
+      </c>
+      <c r="G1823" t="n">
+        <v>0.870000004768372</v>
+      </c>
+      <c r="H1823" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RAD.MI.xlsx
+++ b/data/RAD.MI.xlsx
@@ -42317,7 +42317,9 @@
       <c r="E1824" t="n">
         <v>0.884999990463257</v>
       </c>
-      <c r="F1824"/>
+      <c r="F1824" t="n">
+        <v>0.870000004768372</v>
+      </c>
       <c r="G1824" t="s">
         <v>7</v>
       </c>

--- a/data/RAD.MI.xlsx
+++ b/data/RAD.MI.xlsx
@@ -42386,7 +42386,9 @@
       <c r="E1827" t="n">
         <v>0.855000019073486</v>
       </c>
-      <c r="F1827"/>
+      <c r="F1827" t="n">
+        <v>0.845000028610229</v>
+      </c>
       <c r="G1827" t="s">
         <v>7</v>
       </c>

--- a/data/RAD.MI.xlsx
+++ b/data/RAD.MI.xlsx
@@ -42393,6 +42393,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1828">
+      <c r="A1828" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B1828" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1828" t="n">
+        <v>0.845000028610229</v>
+      </c>
+      <c r="D1828" t="n">
+        <v>0.845000028610229</v>
+      </c>
+      <c r="E1828" t="n">
+        <v>0.845000028610229</v>
+      </c>
+      <c r="F1828" t="n">
+        <v>0.845000028610229</v>
+      </c>
+      <c r="G1828" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B1829" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1829" t="n">
+        <v>0.845000028610229</v>
+      </c>
+      <c r="D1829" t="n">
+        <v>0.845000028610229</v>
+      </c>
+      <c r="E1829" t="n">
+        <v>0.845000028610229</v>
+      </c>
+      <c r="F1829"/>
+      <c r="G1829" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RAD.MI.xlsx
+++ b/data/RAD.MI.xlsx
@@ -42432,8 +42432,31 @@
       <c r="E1829" t="n">
         <v>0.845000028610229</v>
       </c>
-      <c r="F1829"/>
+      <c r="F1829" t="n">
+        <v>0.845000028610229</v>
+      </c>
       <c r="G1829" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1830" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C1830" t="n">
+        <v>0.845000028610229</v>
+      </c>
+      <c r="D1830" t="n">
+        <v>0.829999983310699</v>
+      </c>
+      <c r="E1830" t="n">
+        <v>0.845000028610229</v>
+      </c>
+      <c r="F1830"/>
+      <c r="G1830" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RAD.MI.xlsx
+++ b/data/RAD.MI.xlsx
@@ -42455,8 +42455,31 @@
       <c r="E1830" t="n">
         <v>0.845000028610229</v>
       </c>
-      <c r="F1830"/>
+      <c r="F1830" t="n">
+        <v>0.829999983310699</v>
+      </c>
       <c r="G1830" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1831" t="n">
+        <v>500</v>
+      </c>
+      <c r="C1831" t="n">
+        <v>0.845000028610229</v>
+      </c>
+      <c r="D1831" t="n">
+        <v>0.845000028610229</v>
+      </c>
+      <c r="E1831" t="n">
+        <v>0.845000028610229</v>
+      </c>
+      <c r="F1831"/>
+      <c r="G1831" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RAD.MI.xlsx
+++ b/data/RAD.MI.xlsx
@@ -42478,8 +42478,31 @@
       <c r="E1831" t="n">
         <v>0.845000028610229</v>
       </c>
-      <c r="F1831"/>
+      <c r="F1831" t="n">
+        <v>0.845000028610229</v>
+      </c>
       <c r="G1831" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1832" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C1832" t="n">
+        <v>0.920000016689301</v>
+      </c>
+      <c r="D1832" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="E1832" t="n">
+        <v>0.920000016689301</v>
+      </c>
+      <c r="F1832"/>
+      <c r="G1832" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RAD.MI.xlsx
+++ b/data/RAD.MI.xlsx
@@ -42501,8 +42501,31 @@
       <c r="E1832" t="n">
         <v>0.920000016689301</v>
       </c>
-      <c r="F1832"/>
+      <c r="F1832" t="n">
+        <v>0.850000023841858</v>
+      </c>
       <c r="G1832" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1833" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1833" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="D1833" t="n">
+        <v>0.845000028610229</v>
+      </c>
+      <c r="E1833" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="F1833"/>
+      <c r="G1833" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RAD.MI.xlsx
+++ b/data/RAD.MI.xlsx
@@ -42531,6 +42531,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1834">
+      <c r="A1834" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1834" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C1834" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="D1834" t="n">
+        <v>0.834999978542328</v>
+      </c>
+      <c r="E1834" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="F1834" t="n">
+        <v>0.834999978542328</v>
+      </c>
+      <c r="G1834" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RAD.MI.xlsx
+++ b/data/RAD.MI.xlsx
@@ -48111,6 +48111,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1837">
+      <c r="A1837" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1837" t="n">
+        <v>26500</v>
+      </c>
+      <c r="C1837" t="n">
+        <v>0.879999995231628</v>
+      </c>
+      <c r="D1837" t="n">
+        <v>0.824999988079071</v>
+      </c>
+      <c r="E1837" t="n">
+        <v>0.829999983310699</v>
+      </c>
+      <c r="F1837" t="n">
+        <v>0.829999983310699</v>
+      </c>
+      <c r="G1837" t="n">
+        <v>0.829999983310699</v>
+      </c>
+      <c r="H1837" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RAD.MI.xlsx
+++ b/data/RAD.MI.xlsx
@@ -48137,6 +48137,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1838">
+      <c r="A1838" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1838" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C1838" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="D1838" t="n">
+        <v>0.845000028610229</v>
+      </c>
+      <c r="E1838" t="n">
+        <v>0.845000028610229</v>
+      </c>
+      <c r="F1838" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="G1838" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="H1838" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RAD.MI.xlsx
+++ b/data/RAD.MI.xlsx
@@ -53680,6 +53680,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1839">
+      <c r="A1839" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1839" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1839" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="D1839" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="E1839" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="F1839" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="G1839" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="H1839" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1839" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1840" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1840" t="n">
+        <v>0.829999983310699</v>
+      </c>
+      <c r="D1840" t="n">
+        <v>0.829999983310699</v>
+      </c>
+      <c r="E1840" t="n">
+        <v>0.819999992847443</v>
+      </c>
+      <c r="F1840" t="n">
+        <v>0.829999983310699</v>
+      </c>
+      <c r="G1840" t="n">
+        <v>0.829999983310699</v>
+      </c>
+      <c r="H1840" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I1840" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RAD.MI.xlsx
+++ b/data/RAD.MI.xlsx
@@ -53738,6 +53738,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1841">
+      <c r="A1841" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1841" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1841" t="n">
+        <v>0.839999973773956</v>
+      </c>
+      <c r="D1841" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="E1841" t="n">
+        <v>0.839999973773956</v>
+      </c>
+      <c r="F1841" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="G1841" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="H1841" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I1841" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RAD.MI.xlsx
+++ b/data/RAD.MI.xlsx
@@ -53767,6 +53767,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1842">
+      <c r="A1842" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1842" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1842" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="D1842" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="E1842" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="F1842" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="G1842" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="H1842" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1842" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RAD.MI.xlsx
+++ b/data/RAD.MI.xlsx
@@ -53796,6 +53796,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1843">
+      <c r="A1843" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1843" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1843" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="D1843" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="E1843" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="F1843" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="G1843" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="H1843" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1843" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1844" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1844" t="n">
+        <v>0.855000019073486</v>
+      </c>
+      <c r="D1844" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="E1844" t="n">
+        <v>0.855000019073486</v>
+      </c>
+      <c r="F1844" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="G1844" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="H1844" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I1844" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RAD.MI.xlsx
+++ b/data/RAD.MI.xlsx
@@ -53854,6 +53854,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1845">
+      <c r="A1845" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1845" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1845" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="D1845" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="E1845" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="F1845" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="G1845" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="H1845" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1845" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RAD.MI.xlsx
+++ b/data/RAD.MI.xlsx
@@ -53883,6 +53883,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1846">
+      <c r="A1846" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1846" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1846" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="D1846" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="E1846" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="F1846" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="G1846" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="H1846" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1846" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RAD.MI.xlsx
+++ b/data/RAD.MI.xlsx
@@ -53912,6 +53912,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1847">
+      <c r="A1847" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1847" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1847" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="D1847" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="E1847" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="F1847" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="G1847" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="H1847" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1847" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1848" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1848" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="D1848" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="E1848" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="F1848" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="G1848" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="H1848" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I1848" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
